--- a/output/pdf_financials_xlsx/PXI.xlsx
+++ b/output/pdf_financials_xlsx/PXI.xlsx
@@ -553,10 +553,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.460812</v>
+        <v>0.78298</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.269073</v>
+        <v>0.615471</v>
       </c>
     </row>
     <row r="11">
@@ -566,10 +566,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.06424100000000001</v>
+        <v>-0.386409</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0.659763</v>
+        <v>0.313365</v>
       </c>
     </row>
     <row r="12">
@@ -2047,10 +2047,10 @@
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>0</v>
+        <v>-0.093711</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0</v>
+        <v>-0.095613</v>
       </c>
     </row>
     <row r="125">
@@ -2060,10 +2060,10 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>0</v>
+        <v>-0.093711</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>-0.095613</v>
       </c>
     </row>
     <row r="126">
@@ -3156,7 +3156,11 @@
           <t>Office lease payments</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E36" s="5" t="n">
         <v>-0.093711</v>
       </c>
@@ -3792,14 +3796,14 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>-0.78298</v>
+        <v>0.78298</v>
       </c>
       <c r="F60" s="5" t="n">
-        <v>-0.615471</v>
+        <v>0.615471</v>
       </c>
     </row>
     <row r="61">

--- a/output/pdf_financials_xlsx/PXI.xlsx
+++ b/output/pdf_financials_xlsx/PXI.xlsx
@@ -803,10 +803,10 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0</v>
+        <v>0.075202</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0</v>
+        <v>0.07520300000000001</v>
       </c>
     </row>
     <row r="29">
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.884035</v>
+        <v>0.959237</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>5.220546</v>
+        <v>5.295749</v>
       </c>
     </row>
     <row r="30">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>222.919729380111</v>
+        <v>241.8827902191537</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>562.0525044248931</v>
+        <v>570.1489821669272</v>
       </c>
     </row>
     <row r="31">
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>0.075202</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.07520300000000001</v>
       </c>
     </row>
     <row r="101">
@@ -2888,7 +2888,11 @@
           <t>Depreciation of right-of-use asset</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E26" s="5" t="n">
         <v>0.075202</v>
       </c>

--- a/output/pdf_financials_xlsx/PXI.xlsx
+++ b/output/pdf_financials_xlsx/PXI.xlsx
@@ -514,10 +514,10 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.127222</v>
+        <v>0.139222</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.103656</v>
+        <v>0.127656</v>
       </c>
     </row>
     <row r="8">
@@ -3614,7 +3614,11 @@
           <t>Directors’ fees (note 9)</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E53" s="5" t="n">
         <v>0.012</v>
       </c>
